--- a/doc_converter_app/_sample_inputs/示例表格.xlsx
+++ b/doc_converter_app/_sample_inputs/示例表格.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成员" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成员表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="备注" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -504,25 +504,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>这是第二个工作表的内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>world</t>
         </is>
       </c>
     </row>
